--- a/outputs/Block5_Projection_Reliability.xlsx
+++ b/outputs/Block5_Projection_Reliability.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Component</t>
   </si>
@@ -40,7 +40,10 @@
     <t>Derived Values</t>
   </si>
   <si>
-    <t>High sensitivity</t>
+    <t>Very high sensitivity</t>
+  </si>
+  <si>
+    <t>Moderate-low sensitivity</t>
   </si>
   <si>
     <t>Moderate sensitivity</t>
@@ -438,13 +441,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>45.955</v>
+        <v>26.045</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -452,13 +455,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>66.431</v>
+        <v>78.65300000000001</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -466,13 +469,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>63.918</v>
+        <v>66.76300000000001</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -483,10 +486,10 @@
         <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
